--- a/BWI/bestwine_output/bestwine_El Salvador.xlsx
+++ b/BWI/bestwine_output/bestwine_El Salvador.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA29"/>
+  <dimension ref="A1:AA31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3476,6 +3476,216 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Crio Inversiones S.a. De C.v.</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Crio Inversiones S.a. De C.v.</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>21696</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>San Salvador</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>San Salvador Department</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>716 Avenida La Capilla</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>CP 1101</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crio.com.sv</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>ac@crio.com.sv</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>+503 2133 4800</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/crio-inversiones-s-a-de-c-v-</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/crio.inversiones</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/crio.sv</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>Laura Martínez</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/laura-mart%C3%ADnez-a0b021b3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Crio Inversiones S.a. De C.v.</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Crio Inversiones S.a. De C.v.</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>21696</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>San Salvador</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>San Salvador Department</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>716 Avenida La Capilla</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>CP 1101</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crio.com.sv</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>ac@crio.com.sv</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>+503 2133 4800</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/crio-inversiones-s-a-de-c-v-</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/crio.inversiones</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/crio.sv</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Enrique Palomo Alvarez</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carlos-enrique-palomo-alvarez-294a92190/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_El Salvador.xlsx
+++ b/BWI/bestwine_output/bestwine_El Salvador.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA31"/>
+  <dimension ref="A1:AA33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3686,6 +3686,216 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Crio Inversiones S.a. De C.v.</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Crio Inversiones S.a. De C.v.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>21696</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>San Salvador</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>San Salvador Department</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>716 Avenida La Capilla</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>CP 1101</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crio.com.sv</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>ac@crio.com.sv</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>+503 2133 4800</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/crio-inversiones-s-a-de-c-v-</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/crio.inversiones</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/crio.sv</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>Laura Martínez</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/laura-mart%C3%ADnez-a0b021b3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Crio Inversiones S.a. De C.v.</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Crio Inversiones S.a. De C.v.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>21696</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>San Salvador</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>San Salvador Department</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>716 Avenida La Capilla</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>CP 1101</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crio.com.sv</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>ac@crio.com.sv</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>+503 2133 4800</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/crio-inversiones-s-a-de-c-v-</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/crio.inversiones</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/crio.sv</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Enrique Palomo Alvarez</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carlos-enrique-palomo-alvarez-294a92190/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_El Salvador.xlsx
+++ b/BWI/bestwine_output/bestwine_El Salvador.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA33"/>
+  <dimension ref="A1:AA35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3896,6 +3896,216 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Crio Inversiones S.a. De C.v.</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Crio Inversiones S.a. De C.v.</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>21696</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>San Salvador</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>San Salvador Department</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>716 Avenida La Capilla</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>CP 1101</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crio.com.sv</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>ac@crio.com.sv</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>+503 2133 4800</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/crio-inversiones-s-a-de-c-v-</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/crio.inversiones</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/crio.sv</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr"/>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>Laura Martínez</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/laura-mart%C3%ADnez-a0b021b3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Crio Inversiones S.a. De C.v.</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Crio Inversiones S.a. De C.v.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>21696</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>San Salvador</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>San Salvador Department</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>716 Avenida La Capilla</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>CP 1101</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crio.com.sv</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>ac@crio.com.sv</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>+503 2133 4800</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/crio-inversiones-s-a-de-c-v-</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/crio.inversiones</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/crio.sv</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Enrique Palomo Alvarez</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carlos-enrique-palomo-alvarez-294a92190/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
